--- a/신고신저가_20260828.xlsx
+++ b/신고신저가_20260828.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,15 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 미국 증시에서 소프트웨어 한 섹터만 따로 폭발한 하루였다. 세일즈포스가 연간 이익 가이던스를 크게 올리면서 그동안 "AI가 SaaS를 잡아먹는다"는 서사에 눌려 있던 기업용 소프트웨어 전체가 하루 만에 재평가됐고, 신고가 67종 가운데 30종이 이 섹터에서 나왔다. 반대편에서는 소비재와 유통이 줄줄이 신저가로 밀리며, 돈이 소비에서 소프트웨어로 옮겨 타는 그림이 선명해졌다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/27): 지수 상승은 겉모습이고 실제로는 극단적인 한 섹터 쏠림이었다. S&amp;P500이 0.72%, 나스닥이 1.57% 올랐지만 11개 SPDR 섹터 중 오른 것은 테크(3.2%) 하나뿐이고 나머지 열 개가 모두 내렸다. 세일즈포스가 22.6% 뛰자 옥타 28.6%, 크라우드스트라이크 20.5%, 서비스나우 10.0% 등 소프트웨어 20여 종이 함께 신고가를 냈다. 반면 신저가 25종은 호멜푸드 10.3% 급락을 앞세운 소비재와 유통, 그리고 유틸리티 5종에 몰렸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/27): 은행이 홀로 시장을 끌고 있다. 신고가 6종 중 시즈오카파이낸셜과 스미토모미쓰이트러스트를 포함한 금융이 절반을 차지했고, 금리 상승 기대가 계속 순환매를 만들어내는 중이다. 은행 업종 ETF는 한 주 동안 4.1% 올라 연초 이후 47.8%로 철강에 이은 2위다. 신저가는 니테라 한 종에 그쳐 시장 전반의 훼손은 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/27): 지수는 쉬었지만 개별 재료는 살아 있었다. 항셍이 0.34%, 항셍테크가 0.13% 내리며 이틀째 조용한 흐름이었는데, 한소제약이 상반기 호실적과 외국계 목표주가 상향에 16.0% 급등해 신고가를 냈다. 중신은행도 신고가에 합류했으나 재료는 확인되지 않아 수급으로 본다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/27): AI 관련주가 지수를 밀어 올렸다. 상해종합이 1.13% 오르는 동안 반도체 ETF가 4.5%, 통신이 4.0%, 기술주가 4.3% 뛰며 상승분 대부분을 만들었고, 은행 ETF는 1.2% 내려 자금 이동이 드러났다. 다만 태양광은 정반대로, 양광전원이 미국의 전력망 설비 수입제한 행정명령 여파로 12.2% 급락하며 신저가를 기록했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ① 서비스나우·워크데이 등 후속 소프트웨어 실적에서 세일즈포스만큼의 가이던스 상향이 나오는지 — 하루짜리 안도인지 업종 이익 상향의 시작인지를 가른다. ② 미국 소비재·유통의 신저가가 더 늘어나는지, 특히 가이던스를 내린 곳이 추가로 나오는지를 본다. ③ 트럼프 전력망 설비 행정명령의 적용 범위가 구체화되는 과정 — 중국 태양광·에너지저장주뿐 아니라 미국 전력 설비 공급망 전반에 영향이 번질 수 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 배울점: 세일즈포스는 매출이 11% 늘었을 뿐인데 주가가 22.6% 올랐다. 재료의 본체는 매출이 아니라 연간 조정 EPS 가이던스를 14.06~14.12달러에서 16.67~16.71달러로, 중간값 기준 18.5% 올린 것이었다. 이 숫자가 두 경로를 동시에 건드렸다. 하나는 이익 경로로, 매출 증가폭보다 이익 증가폭이 훨씬 크다는 것은 AI 기능을 붙여도 비용이 그만큼 늘지 않는다는 뜻이다. 다른 하나는 멀티플 경로인데, 그동안 시장은 AI가 소프트웨어 구독을 대체할 것이라 보고 어도비 선행 PER을 11배까지 눌러놨고 그 전제가 한 번에 깨지면서 할인이 풀렸다. 그래서 순수 SaaS일수록 눌림이 컸고 되돌림도 컸다. 옥타가 28.6%로 세일즈포스보다 더 오른 이유가 여기에 있으며, 실적을 발표하지도 않은 아틀라시안과 오토데스크까지 함께 뛴 것이 이것이 개별 실적이 아니라 서사 교체였음을 말해준다. 같은 날 양광전원은 정반대 사례다. 미국이 전력망 설비 수입을 제한하면 이 회사는 미국 매출 자체가 사라지므로, 서사가 아니라 이익 경로가 직접 잘린 것이고 그래서 12.2% 하락에는 되돌림의 여지가 적다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 미국 수치는 한국시간 8월 28일 새벽 5시에 마감한 8월 27일 정규장 기준이며, 일본·홍콩·중국은 8월 27일 마감 확정치다. 종목 PER은 선행 12개월 기준이고, 지수 표의 닛케이225 값만 8월 26일자다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +791,19 @@
       <c r="C2" t="n">
         <v>7730.99</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>5.67</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>2.21</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>12.94</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +829,19 @@
       <c r="C3" t="n">
         <v>26541.35</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>1.57</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>8.58</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>-1.4</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>14.2</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +867,19 @@
       <c r="C4" t="n">
         <v>6808.21</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>5.21</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>-15.4</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>61.56</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +905,19 @@
       <c r="C5" t="n">
         <v>66262.16</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>2.05</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>1.94</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>31.63</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +943,19 @@
       <c r="C6" t="n">
         <v>3956.57</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="4" t="n">
         <v>1.13</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>3.35</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>-2.75</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>-0.31</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +981,19 @@
       <c r="C7" t="n">
         <v>4630.28</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <v>-5.35</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.01</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1019,19 @@
       <c r="C8" t="n">
         <v>25565.74</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>-0.34</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>-0.52</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>2.24</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>-0.25</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1057,19 @@
       <c r="C9" t="n">
         <v>4620.29</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>-0.13</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>-1.71</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="5" t="n">
         <v>-5.02</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <v>-5.49</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>-16.24</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1188,7 @@
       <c r="F2" t="n">
         <v>30</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1229,7 @@
       <c r="F3" t="n">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1270,7 @@
       <c r="F4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1311,7 @@
       <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1352,7 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1393,7 @@
       <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1434,7 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1475,7 @@
       <c r="F9" t="n">
         <v>-1</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1434,7 +1516,7 @@
       <c r="F10" t="n">
         <v>-1</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1475,7 +1557,7 @@
       <c r="F11" t="n">
         <v>-1</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1516,7 +1598,7 @@
       <c r="F12" t="n">
         <v>-2</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1557,7 +1639,7 @@
       <c r="F13" t="n">
         <v>-2</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1598,7 +1680,7 @@
       <c r="F14" t="n">
         <v>-2</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1639,7 +1721,7 @@
       <c r="F15" t="n">
         <v>-5</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +2006,7 @@
       <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2047,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2004,7 +2086,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2043,7 +2125,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2084,7 +2166,7 @@
       <c r="F26" t="n">
         <v>-1</v>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2677,7 +2759,7 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2718,7 +2800,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2759,7 +2841,7 @@
       <c r="F43" t="n">
         <v>-1</v>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3393,7 +3475,7 @@
       <c r="F59" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3432,7 +3514,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3473,7 +3555,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3514,7 +3596,7 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3553,7 +3635,7 @@
       <c r="F63" t="n">
         <v>-1</v>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3594,7 +3676,7 @@
       <c r="F64" t="n">
         <v>-2</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4101,30 +4183,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,90 +4228,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4250,58 +4338,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>당일 +3.2%로 11개 섹터 중 유일한 상승. 소프트웨어 재평가가 지수를 혼자 끌었다</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>31.3</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4321,58 +4414,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>당일 -1.1%지만 3개월 +14.2%로 여전히 상위. 헬스케어 신고가 9종은 유지</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>14.2</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4392,58 +4490,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.7%로 쉬어감. 3개월 +13.3%·신고가 9종으로 추세 자체는 훼손 없음</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4463,58 +4566,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>당일 -1.1%, 연간 -2.6%로 하위권. 벌링턴·타페스트리 등 소비 신저가가 누적된다</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4534,58 +4642,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>당일 -1.1%, 연간 -4.8%로 11개 섹터 꼴찌. 소프트웨어 랠리에서 소외됐다</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4605,58 +4718,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.9%. 신고가 없이 신저가 2종으로 순강도 마이너스, 방향 전환 초입 추정</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4676,58 +4794,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>당일 -1.4%로 최약. 호멜 10% 급락이 상징하듯 가격결정력 훼손이 드러났다</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4747,58 +4870,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.2%로 보합이나 연간 +41.2%로 압도적 1위. 올해 최강 섹터 지위 유지</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>6.2</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>41.2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4818,58 +4946,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.8%, 1개월 -3.9%. 신저가 5종으로 미국 내 최다, AI 전력 테마 냉각 신호</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4889,58 +5022,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.8%지만 주간 +1.5%·연간 +18.3%로 상위. 비에너지광물 신고가 4종이 지지</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4960,58 +5098,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>당일 -1.0%, 1개월 -2.8%. 금리 민감 자산으로 소외 지속</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5031,58 +5174,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>11.1</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5102,58 +5246,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5173,58 +5318,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>6.9</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>13</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5244,58 +5390,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>7</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5315,58 +5462,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>12</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5386,58 +5534,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5457,58 +5606,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-5.3</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>51.3</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5528,58 +5678,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>9</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5599,58 +5750,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>8.9</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>33.1</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5670,58 +5822,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>7.6</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5741,58 +5894,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>14</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5812,58 +5966,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>11</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5883,58 +6038,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,58 +6110,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6025,58 +6182,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>47.8</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6096,58 +6254,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>29.3</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6167,58 +6326,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6238,58 +6398,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-14.4</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-13.5</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6309,58 +6470,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-17.8</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.6</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6380,56 +6542,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-5.1</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-15.8</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6447,58 +6610,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>당일 +4.5%로 A주 최강. 연간 +45.2% 1위, AI 반도체 자립 테마가 여전히 주도</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>45.2</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.2</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6518,58 +6686,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>당일 +4.3%. 반도체·통신과 함께 기술주 3인방이 지수 상승분을 대부분 만들었다</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>-6.6</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>30.2</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6589,58 +6762,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>당일 +4.0%, 1개월 +9.8%. AI 데이터센터 통신 수요 기대가 살아있다</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-12.6</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6660,56 +6838,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>당일 +0.2%로 소외. 3개월 -16.1%·연간 -12.6%로 전기차 체인 부진이 길다</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-16.1</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-12.6</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6727,58 +6910,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>당일 +1.8%. 선양비행기 신고가가 나왔지만 연간 -18.4%로 낙폭 회복은 아직 멀다</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-12.7</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-18.4</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6798,56 +6986,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.6%. 대장주 양광전원이 12% 급락하며 3개월 -21.3%의 부진을 이어갔다</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-21.3</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-12.1</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6865,58 +7058,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.5%, 연간 -21.5%로 13개 중 꼴찌. 내수 소비 회복 지연이 그대로 반영</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-7.9</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-21.5</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>302.8</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6936,58 +7134,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>당일 -1.2%로 최약. 자금이 저평가 은행에서 기술주로 옮겨간 하루로 추정</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7007,58 +7210,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>당일 +1.2%, 주간 +4.4%·1개월 +11.3%. 금속 가격 강세가 꾸준히 반영되고 있다</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>4</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7078,58 +7286,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>당일 +0.7%로 반등했으나 연간 -17.7%. 정책 기대 이상의 실적 근거는 아직 없다</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-8.9</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-17.7</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>11</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7149,58 +7362,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>당일 +0.9%, 주간 +4.0%. 거래대금 회복 기대가 붙는 전형적 지수 상승 동행</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7220,58 +7438,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>당일 +0.5%지만 주간 -3.5%로 조정. 3개월 +12.2%의 상승분을 되돌리는 국면</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7291,58 +7514,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>당일 보합, 연간 -16.1%. 미국 소비재 신저가와 같은 방향으로 소비 약세가 확인된다</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-16.1</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7354,7 +7582,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1.4"/>
@@ -7366,7 +7594,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-3.5"/>
@@ -7378,7 +7606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-4.9"/>
@@ -7390,7 +7618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-21.3"/>
@@ -7402,7 +7630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-21.5"/>
@@ -7414,7 +7642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7426,7 +7654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7438,7 +7666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7450,7 +7678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7462,7 +7690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7474,7 +7702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7588,12 +7816,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7637,15 +7865,15 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7691,15 +7919,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>크라우드스트라이크(사이버보안 SaaS): 2분기 실적·가이던스 서프라이즈, 보안지출 확대 부각</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7743,15 +7975,19 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>세일즈포스(기업용 CRM SaaS): 2분기 매출 11% 증가에 연간 EPS 가이던스 중간값 18% 상향</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7795,15 +8031,15 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7849,15 +8085,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7901,10 +8137,10 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7955,19 +8191,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>(전일) TJX컴퍼니스(오프프라이스 의류 유통): 분기 실적은 상회했으나 가이던스가 보수적</t>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>TJX(티제이맥스·마셜스 할인 유통): 마막스 부문 둔화를 짚은 투자의견 하향 여파</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8011,15 +8247,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>서비스나우(기업 업무자동화 플랫폼): 세일즈포스 호실적에 대형 소프트웨어 동반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8067,15 +8307,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>포티넷(네트워크 보안 장비·소프트웨어): 보안 지출 확대 기대에 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8119,15 +8363,19 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>어도비(크리에이티브·문서 소프트웨어): 선행 PER 11배 저평가 부각되며 섹터 랠리에 동반</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8171,15 +8419,15 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8223,10 +8471,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8275,10 +8523,10 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8327,15 +8575,15 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8379,15 +8627,15 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8427,15 +8675,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8479,10 +8727,14 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>오토데스크(설계·엔지니어링 소프트웨어): 소프트웨어 섹터 랠리 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8535,14 +8787,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>(전일) 나이키(스포츠화·의류): 대형 투자은행이 투자의견 비중축소로 하향, 재건 비용 우려</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8591,15 +8843,15 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8647,15 +8899,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8703,15 +8955,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8753,10 +9005,10 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8805,15 +9057,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8857,15 +9109,15 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8909,15 +9161,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8963,15 +9215,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>아틀라시안(지라·컨플루언스 협업 도구): 세일즈포스발 SaaS 재평가에 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9013,15 +9269,19 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>비바시스템즈(제약·바이오 전용 클라우드): 2분기 실적 호조에 소프트웨어 랠리 동반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9065,15 +9325,15 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9117,15 +9377,15 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9173,10 +9433,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9229,10 +9489,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9279,19 +9539,19 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="8" t="inlineStr">
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>(전일) 페로비알(유료도로·공항 인프라 운영): 특별한 뉴스 없음(개별 약세 지속)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9335,15 +9595,15 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9391,10 +9651,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9443,14 +9703,14 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="8" t="inlineStr">
+      <c r="N36" s="10" t="inlineStr">
         <is>
           <t>(전일) (프레스티지 화장품) 분기 EPS 서프라이즈와 중국 매출 회복에 목표가 줄상향</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9503,19 +9763,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="8" t="inlineStr">
+      <c r="N37" s="10" t="inlineStr">
         <is>
           <t>(전일) (유전체 시퀀싱 장비) 2분기 매출 서프라이즈 여진에 신고가 지속</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9559,15 +9819,15 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9615,15 +9875,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>옥타(기업용 신원인증 SaaS): 2분기 실적 상회·가이던스 상향, 소프트웨어 동반 랠리로 급등</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9671,15 +9935,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>라스베가스샌즈(마카오·싱가포르 카지노 리조트): 특별한 뉴스 없음, 마카오 회복 둔화 우려 지속</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9723,15 +9991,15 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9779,15 +10047,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9831,15 +10099,15 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9887,15 +10155,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9943,10 +10211,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9999,15 +10267,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N46" s="8" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10051,15 +10319,19 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>태피스트리(코치·케이트스페이드 보유 패션그룹): 자체 재료 아닌 유통업종 동반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10103,15 +10375,15 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10155,10 +10427,10 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10207,15 +10479,15 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="8" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10259,15 +10531,15 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10311,15 +10583,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N52" s="8" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr">
+        <is>
+          <t>루브릭(데이터 백업·복구 SaaS): 소프트웨어 섹터 재평가에 동반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10363,15 +10639,15 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="8" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10415,15 +10691,15 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" s="8" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10467,15 +10743,15 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10517,15 +10793,15 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="8" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10567,15 +10843,19 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="8" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>벌링턴스토어스(할인 의류 유통): 2분기 매출 컨센 미달, 동일점포매출 둔화 부각</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10623,10 +10903,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="8" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10679,14 +10959,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="8" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>(전일) 플레인스올아메리칸(원유 파이프라인 MLP): 개별 재료 없음, 에너지·산업재 섹터 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10739,15 +11019,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N60" s="8" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr">
+        <is>
+          <t>뉴스코프(다우존스·부동산정보 보유 미디어 지주): 특별한 뉴스 없음, 지수 강세 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10791,10 +11075,10 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" s="8" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10847,15 +11131,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N62" s="8" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10903,15 +11187,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N63" s="8" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10955,15 +11239,15 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11011,15 +11295,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="8" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11061,15 +11345,15 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="8" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11113,15 +11397,15 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11163,10 +11447,14 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr">
+        <is>
+          <t>피그마(디자인 협업 SaaS): 2분기 매출 48% 증가 서프라이즈, 연간 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11213,15 +11501,15 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11263,15 +11551,15 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11319,15 +11607,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N71" s="8" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11371,15 +11659,15 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="8" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11423,10 +11711,10 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="8" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11477,15 +11765,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="8" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11531,10 +11819,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="8" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11587,15 +11875,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N76" s="8" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11639,15 +11927,15 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="8" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11693,10 +11981,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N78" s="8" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11749,14 +12037,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N79" s="8" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>(전일) 스머커(잼·커피·펫푸드 식품): 분기 매출·이익 서프라이즈에 연간 이익 가이던스 상향</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11805,10 +12093,10 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="8" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11861,15 +12149,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N81" s="8" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr">
+        <is>
+          <t>맨해튼어소시에이츠(공급망관리 SaaS): 자체 재료 아닌 소프트웨어 섹터 랠리 편승 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11915,15 +12207,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N82" s="8" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr">
+        <is>
+          <t>제이프로그(소프트웨어 배포·저장소 관리): 섹터 전반 랠리 편승, 개별 재료 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11967,15 +12263,15 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12021,15 +12317,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N84" s="8" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12073,15 +12369,15 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" s="8" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12125,15 +12421,19 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t>데커스아웃도어(호카·어그 신발 브랜드): 마진·관세 우려에 유통업종 동반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12175,15 +12475,19 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" s="8" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr">
+        <is>
+          <t>호멜푸드(스팸 등 육가공 식품): 3분기 매출 컨센 미달에 연간 매출 가이던스 하향</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12225,15 +12529,19 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" s="8" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr">
+        <is>
+          <t>세일포인트(기업용 계정권한 관리 SaaS): 소프트웨어 섹터 전반 재평가에 동반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12277,15 +12585,15 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="8" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12329,15 +12637,15 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" s="8" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12385,10 +12693,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N91" s="8" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12441,15 +12749,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N92" s="8" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12493,7 +12801,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N93" s="8" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N93"/>
@@ -12599,7 +12907,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12652,14 +12960,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 리크루트홀딩스(구인구직 플랫폼·인재파견): 증권사 두 곳이 목표주가를 2만엔 안팎으로 상향</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12706,14 +13014,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 패스트리테일링(유니클로 모기업): 개별 악재 없음, 지수 기여 상위주 차익실현</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12762,14 +13070,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 이토추상사(종합상사): 3000억엔 자사주매입·사상최대 순이익 모멘텀 지속, 상사 섹터 강세</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12818,15 +13126,15 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12874,15 +13182,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>스미토모미쓰이트러스트그룹(신탁은행 지주): 장기금리 상승 기대에 은행·신탁 동반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12930,10 +13242,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>시즈오카파이낸셜그룹(시즈오카현 기반 지방은행 지주): 금리 상승 기대에 지방은행 순환매 지속</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12984,19 +13300,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 젠쇼홀딩스(스키야·하마즈시 외식 체인): 초밥 사업 호조로 연매출 11%·순이익 17% 증가</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13038,7 +13354,11 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>니테라(점화플러그 등 자동차부품): 특별한 뉴스 없음, 미국 부품사업 철수 여진 추정</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N9"/>
@@ -13144,12 +13464,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13193,15 +13513,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>중신은행(중국 대형 국유 상업은행): 특별한 뉴스 없음, 은행주 수급 흐름 추정</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13243,10 +13567,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>한소제약(중국 항암·중추신경 혁신신약 개발사): 상반기 호실적에 외국계 목표주가 상향</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13297,7 +13625,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 창청자동차(중국 SUV·픽업 완성차): 상반기 순이익 61% 급감, 마진 훼손 우려로 신저가</t>
         </is>
@@ -13407,12 +13735,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13458,15 +13786,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>양광전원(태양광 인버터·에너지저장 세계 1위): 미국 전력망 설비 수입제한 행정명령에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13508,10 +13840,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>룽성석유화학(정유·석유화학 대기업): 중동 긴장에 따른 유가 상승 전망으로 정유화학 강세</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13560,19 +13896,19 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 헝리유압(굴착기용 유압부품): 특별한 뉴스 없음, 건설기계 섹터 조정 흐름 추정</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13614,15 +13950,19 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>중항선양비행기(전투기 등 군용 항공기 제조): 특별한 뉴스 없음, 방산 수급 흐름 추정</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13664,10 +14004,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>웨이싱화학(에탄 분해 기반 석유화학): 유가 상승 전망과 과잉경쟁 억제 정책 기대가 겹쳤다</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13714,14 +14058,14 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 상하이농촌상업은행(상하이 지역 상업은행): 낮은 PBR·높은 배당에 보험자금 유입, 연속 신고가</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13770,7 +14114,7 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 저장신허(비타민·정밀화학 생산): 개별 악재 미확인, 화학·성장주 동반 약세 추정</t>
         </is>
